--- a/РАБОЧИЙ СТОЛ/машины Останкино КИ и ЗПФ.xlsx
+++ b/РАБОЧИЙ СТОЛ/машины Останкино КИ и ЗПФ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6829B6-DF76-43A8-95C1-B3FAF2042691}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B40BE74-7257-404F-A13D-1F65099DBE95}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
   <si>
     <t>Бердянск</t>
   </si>
@@ -109,6 +109,12 @@
   </si>
   <si>
     <t>вт</t>
+  </si>
+  <si>
+    <t>Мариуполь</t>
+  </si>
+  <si>
+    <t>Мароиуполь ЗПФ</t>
   </si>
 </sst>
 </file>
@@ -550,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -615,7 +621,7 @@
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6">
-        <f t="shared" ref="F4:F13" si="1">B4-C4-D4-E4</f>
+        <f t="shared" ref="F4:F15" si="1">B4-C4-D4-E4</f>
         <v>0</v>
       </c>
       <c r="G4" s="7" t="s">
@@ -639,34 +645,40 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="A6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="A7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -676,13 +688,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G8" t="s">
-        <v>17</v>
-      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -694,123 +703,152 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G10" s="9" t="s">
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G11" s="9" t="s">
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="4">
-        <f>SUM(B2:B13)</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="4">
-        <f>SUM(C2:C13)</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="4">
-        <f>SUM(D2:D13)</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="4">
-        <f>SUM(E2:E13)</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="4">
-        <f>SUM(F2:F13)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C15" t="s">
+      <c r="B16" s="4">
+        <f>SUM(B2:B15)</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="4">
+        <f>SUM(C2:C15)</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="4">
+        <f>SUM(D2:D15)</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="4">
+        <f>SUM(E2:E15)</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="4">
+        <f>SUM(F2:F15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
         <v>23</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D17" t="s">
         <v>24</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E17" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="10" t="s">
+    <row r="18" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C18" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="12"/>
-    </row>
-    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C17" s="3">
-        <f>IF(ROUNDUP(C14/500,0)&gt;32,32,ROUNDUP(C14/500,0))</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="3">
-        <f t="shared" ref="D17:E17" si="2">IF(ROUNDUP(D14/500,0)&gt;32,32,ROUNDUP(D14/500,0))</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="3">
+      <c r="D18" s="11"/>
+      <c r="E18" s="12"/>
+    </row>
+    <row r="19" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C19" s="3">
+        <f>IF(ROUNDUP(C16/500,0)&gt;32,32,ROUNDUP(C16/500,0))</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="3">
+        <f t="shared" ref="D19:E19" si="2">IF(ROUNDUP(D16/500,0)&gt;32,32,ROUNDUP(D16/500,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C18:E18"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/РАБОЧИЙ СТОЛ/машины Останкино КИ и ЗПФ.xlsx
+++ b/РАБОЧИЙ СТОЛ/машины Останкино КИ и ЗПФ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B40BE74-7257-404F-A13D-1F65099DBE95}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECB3320C-1025-45A3-B004-57CCC7B3F428}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
   <si>
     <t>Бердянск</t>
   </si>
@@ -115,6 +115,12 @@
   </si>
   <si>
     <t>Мароиуполь ЗПФ</t>
+  </si>
+  <si>
+    <t>в третью машину Крыма</t>
+  </si>
+  <si>
+    <t>САП 29,07</t>
   </si>
 </sst>
 </file>
@@ -145,7 +151,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -170,6 +176,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -256,7 +268,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -276,6 +288,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -556,17 +574,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.85546875" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
@@ -583,10 +602,13 @@
         <v>20</v>
       </c>
       <c r="F1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -594,12 +616,13 @@
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="2">
-        <f t="shared" ref="F2:F3" si="0">B2-C2-D2-E2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F2" s="2"/>
+      <c r="G2" s="2">
+        <f>B2-C2-D2-E2-F2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -607,12 +630,13 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
-      <c r="F3" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F3" s="2"/>
+      <c r="G3" s="2">
+        <f t="shared" ref="G3:G15" si="0">B3-C3-D3-E3-F3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>0</v>
       </c>
@@ -620,15 +644,16 @@
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
-      <c r="F4" s="6">
-        <f t="shared" ref="F4:F15" si="1">B4-C4-D4-E4</f>
-        <v>0</v>
-      </c>
-      <c r="G4" s="7" t="s">
+      <c r="F4" s="6"/>
+      <c r="G4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>13</v>
       </c>
@@ -636,47 +661,50 @@
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
-      <c r="F5" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G5" s="7" t="s">
+      <c r="F5" s="6"/>
+      <c r="G5" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
@@ -684,12 +712,13 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
-      <c r="F8" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F8" s="2"/>
+      <c r="G8" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
@@ -697,12 +726,13 @@
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
-      <c r="F9" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F9" s="2"/>
+      <c r="G9" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>2</v>
       </c>
@@ -710,15 +740,16 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="F10" s="2"/>
+      <c r="G10" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
@@ -726,12 +757,13 @@
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
-      <c r="F11" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F11" s="2"/>
+      <c r="G11" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>3</v>
       </c>
@@ -739,15 +771,16 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
-      <c r="F12" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G12" s="9" t="s">
+      <c r="F12" s="8"/>
+      <c r="G12" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>16</v>
       </c>
@@ -755,15 +788,16 @@
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
-      <c r="F13" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="9" t="s">
+      <c r="F13" s="8"/>
+      <c r="G13" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
@@ -771,12 +805,13 @@
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F14" s="2"/>
+      <c r="G14" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
@@ -784,12 +819,13 @@
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F15" s="2"/>
+      <c r="G15" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>12</v>
       </c>
@@ -809,12 +845,13 @@
         <f>SUM(E2:E15)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="4">
-        <f>SUM(F2:F15)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F16" s="4"/>
+      <c r="G16" s="4">
+        <f>SUM(G2:G15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
         <v>23</v>
       </c>
@@ -825,26 +862,28 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C18" s="10" t="s">
         <v>11</v>
       </c>
       <c r="D18" s="11"/>
       <c r="E18" s="12"/>
-    </row>
-    <row r="19" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="F18" s="15"/>
+    </row>
+    <row r="19" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C19" s="3">
         <f>IF(ROUNDUP(C16/500,0)&gt;32,32,ROUNDUP(C16/500,0))</f>
         <v>0</v>
       </c>
       <c r="D19" s="3">
-        <f t="shared" ref="D19:E19" si="2">IF(ROUNDUP(D16/500,0)&gt;32,32,ROUNDUP(D16/500,0))</f>
+        <f t="shared" ref="D19:E19" si="1">IF(ROUNDUP(D16/500,0)&gt;32,32,ROUNDUP(D16/500,0))</f>
         <v>0</v>
       </c>
       <c r="E19" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/РАБОЧИЙ СТОЛ/машины Останкино КИ и ЗПФ.xlsx
+++ b/РАБОЧИЙ СТОЛ/машины Останкино КИ и ЗПФ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECB3320C-1025-45A3-B004-57CCC7B3F428}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{506733A1-E437-483D-AD8A-70D4D539424A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -114,13 +114,13 @@
     <t>Мариуполь</t>
   </si>
   <si>
-    <t>Мароиуполь ЗПФ</t>
-  </si>
-  <si>
     <t>в третью машину Крыма</t>
   </si>
   <si>
     <t>САП 29,07</t>
+  </si>
+  <si>
+    <t>Мариуполь ЗПФ</t>
   </si>
 </sst>
 </file>
@@ -279,6 +279,12 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -288,12 +294,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -602,7 +602,7 @@
         <v>20</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>10</v>
@@ -671,37 +671,37 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>28</v>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -863,12 +863,12 @@
       </c>
     </row>
     <row r="18" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="12"/>
     </row>
     <row r="19" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C19" s="3">
@@ -883,7 +883,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F19" s="16"/>
+      <c r="F19" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">
